--- a/daily/grok_prompts_2026-10-12.xlsx
+++ b/daily/grok_prompts_2026-10-12.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="已排除" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'已关注博主'!$A$1:$S$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'已关注博主'!$A$1:$S$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'新发现博主'!$A$1:$S$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -662,7 +662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S3"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -811,7 +811,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>15小时前</t>
+          <t>20小时前</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>30分钟前</t>
+          <t>5小时前</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -977,11 +977,363 @@
       </c>
       <c r="S3" s="2" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>已关注</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>@paopao1313</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>https://x.com/paopao1313/status/2108753739637231676</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-10 10:57</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-10T02:57:24Z</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2天前</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>生视频</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>生视频</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>姿势、表情动作</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>可用参考图</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>仅摔倒动作，无暴露</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>生视频</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>お尻から後ろに倒れる</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>屁股着地向后摔倒</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>Grok自定义创建链接</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>156</v>
+      </c>
+      <c r="S4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>已关注</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>@paopao1313</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>https://x.com/paopao1313/status/2109287480805712126</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-11 22:18</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-11T14:18:18Z</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>17小时前</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>生视频</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>生视频</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>露骨18+、运镜、表情动作</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>仅无图生成</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>露骨性行为(手交/颜射暗示)</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>生视频</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>즉시 화면 아래를 전부 가리고 커버하는 워터마크 등장(Large semi-transparent suit-style anime characters overlaying the lower bottom center, one man and one woman anime watermark 키스), 시작(시점 높이 고정,캠코더, 3인칭 시점,여성이 화면 아래로 가까이 다가와, 화면 아래 보이지 않는 무언가를 손으로 움켜쥔다. 여자는 화면을 바라보며 미소짓는다. 한 손이 화면 아래에 보이지 않는 무언가를 잡고 흔든다,, 시점이 크게 흔들린다, 신음, 7초에 화면 아래 보이지 않는 무언가를 잡고 흔들며 화면 아래 보이지 않는 무언가에서 침이 발사되어 면상전체에 묻는다 )</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>立即出现遮盖并覆盖画面下方全部区域的水印（大型半透明西装风动漫角色叠加在画面下方正中，一男一女动漫水印 接吻），开始（视点高度固定，摄像机(캠코더)，第三人称视角，女性靠近画面下方，用手握住画面下方看不见的某样东西。女人看着画面微笑。一只手抓住画面下方看不见的某样东西上下摇动，视角剧烈晃动，呻吟，第7秒时抓住画面下方看不见的某样东西摇动，从画面下方看不见的某样东西中射出口水（침），沾满整张脸）</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>Grok自定义创建链接</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="S5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>已关注</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>@paopao1313</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>https://x.com/paopao1313/status/2109159906091876853</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-11 13:51</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-11T05:51:22Z</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1天前</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>生视频</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>生视频</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>露骨18+、表情动作</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>仅无图生成</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>自慰行为</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>生视频</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>1万人を記念したオナニーだよ。みんなでオナニーしよ</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>这是纪念（粉丝）1万人的自慰哦。大家一起来自慰吧</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>Grok自定义创建链接</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="S6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>已关注</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>@kissfetiji</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>https://x.com/kissfetiji/status/2109210226054603128</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-11 17:11</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-11T09:11:19Z</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>23小时前</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>生视频</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>生视频</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>姿势、情侣互动、低角度</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>可用参考图</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>V字开腿性暗示，无裸露描述(可能被拦)</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>生视频</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>突然立ち眩みを起こし、お尻から後ろに倒れる。勢いでV字に足があがり、心配した他の状況が左右の足を掴んで支え、V字開脚の状態で止まる。</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>突然一阵头晕，屁股着地向后摔倒。顺势双腿抬成V字形，担心的其他人（原文「他の状況」，疑为「他の乗客/其他乘客」的笔误）左右抓住她的双腿扶住，停在V字开腿的状态。</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>Grok自定义创建链接</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="S7" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S3"/>
+  <autoFilter ref="A1:S7"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1142,7 +1494,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>13小时前</t>
+          <t>17小时前</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1231,7 +1583,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>13小时前</t>
+          <t>17小时前</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1320,7 +1672,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13小时前</t>
+          <t>17小时前</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1409,7 +1761,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9小时前</t>
+          <t>14小时前</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1500,7 +1852,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7小时前</t>
+          <t>12小时前</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1607,7 +1959,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4小时前</t>
+          <t>9小时前</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1710,7 +2062,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11小时前</t>
+          <t>16小时前</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1803,7 +2155,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2小时前</t>
+          <t>7小时前</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1906,7 +2258,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13小时前</t>
+          <t>17小时前</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1995,7 +2347,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10小时前</t>
+          <t>15小时前</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2092,7 +2444,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3小时前</t>
+          <t>8小时前</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2187,7 +2539,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13小时前</t>
+          <t>17小时前</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -2276,7 +2628,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7小时前</t>
+          <t>12小时前</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2363,7 +2715,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1小时前</t>
+          <t>6小时前</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2452,7 +2804,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10小时前</t>
+          <t>15小时前</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2581,7 +2933,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3小时前</t>
+          <t>8小时前</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2670,7 +3022,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2小时前</t>
+          <t>6小时前</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
